--- a/artfynd/S 1278-2025 artfynd.xlsx
+++ b/artfynd/S 1278-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3377,49 +3377,61 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118883036</v>
+        <v>136125996</v>
       </c>
       <c r="B26" t="n">
-        <v>99140</v>
+        <v>99294</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kullarna, Hls</t>
+          <t>Storstenarna, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>535561</v>
+        <v>535330</v>
       </c>
       <c r="R26" t="n">
-        <v>6829696</v>
+        <v>6829850</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3446,12 +3458,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>16 i blom</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3478,58 +3495,58 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118883036</t>
+          <t>https://artportalen.se/Sighting/136125996</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122031050</v>
+        <v>118883036</v>
       </c>
       <c r="B27" t="n">
-        <v>79085</v>
+        <v>99140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Öratjärn, Hls</t>
+          <t>Kullarna, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>536318</v>
+        <v>535561</v>
       </c>
       <c r="R27" t="n">
-        <v>6828980</v>
+        <v>6829696</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3553,17 +3570,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,30 +3584,31 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustav Forsblom</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustav Forsblom</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122031050</t>
+          <t>https://artportalen.se/Sighting/118883036</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122031051</v>
+        <v>122031050</v>
       </c>
       <c r="B28" t="n">
         <v>79085</v>
@@ -3634,10 +3647,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>536013</v>
+        <v>536318</v>
       </c>
       <c r="R28" t="n">
-        <v>6829230</v>
+        <v>6828980</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3699,6 +3712,117 @@
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122031050</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122031051</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Öratjärn, Hls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>536013</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6829230</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/122031051</t>
         </is>
@@ -3733,6 +3857,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1278-2025 artfynd.xlsx
+++ b/artfynd/S 1278-2025 artfynd.xlsx
@@ -3380,7 +3380,7 @@
         <v>136125996</v>
       </c>
       <c r="B26" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1278-2025 artfynd.xlsx
+++ b/artfynd/S 1278-2025 artfynd.xlsx
@@ -3380,7 +3380,7 @@
         <v>136125996</v>
       </c>
       <c r="B26" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1278-2025 artfynd.xlsx
+++ b/artfynd/S 1278-2025 artfynd.xlsx
@@ -3380,7 +3380,7 @@
         <v>136125996</v>
       </c>
       <c r="B26" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 1278-2025 artfynd.xlsx
+++ b/artfynd/S 1278-2025 artfynd.xlsx
@@ -3380,7 +3380,7 @@
         <v>136125996</v>
       </c>
       <c r="B26" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
